--- a/Data/Solar_Budget.xlsx
+++ b/Data/Solar_Budget.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -503,11 +503,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Mag</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -516,11 +516,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Giu</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
